--- a/02_DIA_inicio_2026_analisis_assets/rbd_9719_escuela-basica-santa-olga-de-kiev_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9719_escuela-basica-santa-olga-de-kiev_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F03BD8B-3D84-4CD8-872D-A0AD69A62C65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C775E0CD-1CF4-4A55-8B6D-58090CEC6A75}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CFA348C-EB11-437F-B622-A0E3667BE548}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{604957CC-7492-4E09-90B1-BFC8272007F9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8FA8FB2-B096-44F3-9B6E-13F45640BDB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE7562CF-BF1B-45F4-826C-C52D901F422B}"/>
 </file>